--- a/書式.xlsx
+++ b/書式.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\プロジェクト\賞与査定\2026年夏季賞与\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9829D55A-0F0A-4483-89D6-4E74D62BC9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255238DC-5598-4643-B70B-2D1F24D35847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="1695" windowWidth="14445" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-210" yWindow="1545" windowWidth="17805" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>総務部</t>
   </si>
   <si>
     <t>主事補</t>
-  </si>
-  <si>
-    <t>令和7年10月～令和8年3月 評価</t>
   </si>
   <si>
     <t>B+</t>
@@ -63,63 +60,63 @@
     <rPh sb="5" eb="9">
       <t>ショウヨサテイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>社員番号</t>
     <rPh sb="0" eb="4">
       <t>シャインバンゴウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
       <t>シメイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>所属部署</t>
     <rPh sb="0" eb="4">
       <t>ショゾクブショ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>役職</t>
     <rPh sb="0" eb="2">
       <t>ヤクショク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>職能</t>
     <rPh sb="0" eb="2">
       <t>ショクノウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>等級</t>
     <rPh sb="0" eb="2">
       <t>トウキュウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>自己評価</t>
     <rPh sb="0" eb="4">
       <t>ジコヒョウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>最終評価</t>
     <rPh sb="0" eb="4">
       <t>サイシュウヒョウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>総合評価</t>
@@ -129,42 +126,35 @@
     <rPh sb="2" eb="4">
       <t>ヒョウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>職能</t>
-    <rPh sb="0" eb="2">
-      <t>ショクノウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>業績</t>
     <rPh sb="0" eb="2">
       <t>ギョウセキ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>基本月数</t>
     <rPh sb="0" eb="4">
       <t>キホンツキスウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>評価</t>
     <rPh sb="0" eb="2">
       <t>ヒョウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>出勤率</t>
     <rPh sb="0" eb="3">
       <t>シュッキンリツ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>調整加減</t>
@@ -174,38 +164,28 @@
     <rPh sb="2" eb="4">
       <t>カゲン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>支給月数</t>
     <rPh sb="0" eb="4">
       <t>シキュウツキスウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>基本給</t>
     <rPh sb="0" eb="3">
       <t>キホンキュウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>支給金額</t>
     <rPh sb="0" eb="4">
       <t>シキュウキンガク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>総合評価</t>
-    <rPh sb="0" eb="2">
-      <t>ソウゴウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウカ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>評価加減</t>
@@ -215,7 +195,7 @@
     <rPh sb="2" eb="4">
       <t>カゲン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>営業日数</t>
@@ -228,7 +208,7 @@
     <rPh sb="3" eb="4">
       <t>ザイニチ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>在籍日数</t>
@@ -238,7 +218,7 @@
     <rPh sb="2" eb="4">
       <t>ニッスウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>欠勤日数</t>
@@ -248,43 +228,45 @@
     <rPh sb="2" eb="4">
       <t>ニッスウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>特記事項　（調整加減理由等）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>課長</t>
+    <rPh sb="0" eb="2">
+      <t>カチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大谷　翔平</t>
+    <rPh sb="0" eb="2">
+      <t>オオタニ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヘイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特記事項</t>
     <rPh sb="0" eb="4">
       <t>トッキジコウ</t>
     </rPh>
-    <rPh sb="6" eb="8">
-      <t>チョウセイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カゲン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>リユウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>トウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課長</t>
-    <rPh sb="0" eb="2">
-      <t>カチョウ</t>
-    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>令和7年10月～令和8年3月 評価</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>大谷　翔平</t>
-    <rPh sb="0" eb="2">
-      <t>オオタニ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ショウヘイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+    <t>出勤状況</t>
+    <rPh sb="0" eb="2">
+      <t>シュッキン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -294,7 +276,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,15 +292,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
@@ -326,11 +299,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <sz val="10"/>
+      <color rgb="FF1E1E1E"/>
+      <name val="BIZ UDPゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E1E1E"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -343,13 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FF2980B9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFD6E6F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,106 +367,80 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0AAB4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0AAB4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -475,14 +449,14 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
       </left>
       <right/>
       <top/>
@@ -492,156 +466,209 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFA0AAB4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0AAB4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0AAB4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA0AAB4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0AAB4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0AAB4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFA0AAB4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0AAB4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA0AAB4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFA0AAB4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0AAB4"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="58" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -649,6 +676,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFD6E6F2"/>
+      <color rgb="FFCCECFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -923,310 +957,403 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" customWidth="1"/>
+    <col min="5" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:11" ht="18.75">
+      <c r="A1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="48">
+        <v>46188</v>
+      </c>
+      <c r="K1" s="47"/>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3">
-        <v>46188</v>
-      </c>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="39" t="s">
+      <c r="B3" s="7">
+        <v>233</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="33">
-        <v>233</v>
-      </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="39" t="s">
+      <c r="E3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A4" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="38"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="39" t="s">
+      <c r="B4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="E4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="18">
+        <v>2</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A7" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="23"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" customHeight="1"/>
+    <row r="11" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+    </row>
+    <row r="12" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A12" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A13" s="45"/>
+      <c r="B13" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+    </row>
+    <row r="14" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A14" s="37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="12">
+        <v>100</v>
+      </c>
+      <c r="E14" s="12">
+        <v>100</v>
+      </c>
+      <c r="F14" s="12">
+        <v>5</v>
+      </c>
+      <c r="G14" s="39">
+        <v>0.95</v>
+      </c>
+      <c r="H14" s="12">
         <v>0</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="17"/>
-      <c r="B14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="I14" s="12">
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="J14" s="38">
+        <v>287100</v>
+      </c>
+      <c r="K14" s="40">
+        <v>655000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+    </row>
+    <row r="17" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="19">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="19">
-        <v>0.2</v>
-      </c>
-      <c r="D15" s="20">
-        <v>100</v>
-      </c>
-      <c r="E15" s="20">
-        <v>100</v>
-      </c>
-      <c r="F15" s="20">
-        <v>5</v>
-      </c>
-      <c r="G15" s="21">
-        <v>0.95</v>
-      </c>
-      <c r="H15" s="22">
-        <v>0</v>
-      </c>
-      <c r="I15" s="22">
-        <v>2.2800000000000002</v>
-      </c>
-      <c r="J15" s="23">
-        <v>287100</v>
-      </c>
-      <c r="K15" s="24">
-        <v>655000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="27"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="28"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="29"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="28"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="29"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="28"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="29"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="28"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="29"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="32"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="28"/>
+    </row>
+    <row r="19" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="28"/>
+    </row>
+    <row r="20" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="28"/>
+    </row>
+    <row r="21" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="28"/>
+    </row>
+    <row r="22" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="H1:I1"/>
+  <mergeCells count="20">
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="K12:K13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.31496062992125989" right="0.31496062992125989" top="0.39370078740157477" bottom="5.9055118110236222" header="0.19685039370078738" footer="0.19685039370078738"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>